--- a/results/feature_selection/global_ind/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/rP/metrics_global.xlsx
@@ -483,73 +483,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, mu, Plag1, X_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, T, mu, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9526729502478366</v>
+        <v>0.9524801128948442</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02882517399641473</v>
+        <v>0.02999834286910062</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001827590592646152</v>
+        <v>0.001835037237515951</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04275032856769818</v>
+        <v>0.04283733462198543</v>
       </c>
       <c r="H2" t="n">
-        <v>165.0889150368772</v>
+        <v>247.8425504667002</v>
       </c>
       <c r="I2" t="n">
-        <v>-305.8473533748186</v>
+        <v>-313.6359062473784</v>
       </c>
       <c r="J2" t="n">
-        <v>-284.3836724704229</v>
+        <v>-299.9772002173085</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, T, mu, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, Xlag1, Xlag1_calc, Plag1, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9522531803102116</v>
+        <v>0.9523220670632249</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03011343089051402</v>
+        <v>0.02923380182802295</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001843800510507008</v>
+        <v>0.001841140366204242</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0429394982563491</v>
+        <v>0.04290851158225186</v>
       </c>
       <c r="H3" t="n">
-        <v>242.9349598152382</v>
+        <v>168.4311752424794</v>
       </c>
       <c r="I3" t="n">
-        <v>-309.3881698215529</v>
+        <v>-307.4632470249061</v>
       </c>
       <c r="J3" t="n">
-        <v>-291.82697635432</v>
+        <v>-287.9508098390918</v>
       </c>
     </row>
     <row r="4">
@@ -559,33 +559,33 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>X, S, V, P, T, I, mu, dXdt, dSdt, dVdt, Xlag1, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>X, V, P, T, I, mu, dXdt, dVdt, Xlag1, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9506043093950779</v>
+        <v>0.9506224469700126</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03117045943576681</v>
+        <v>0.03126938980442491</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001907473631666402</v>
+        <v>0.001906773227531814</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04367463373248139</v>
+        <v>0.04366661456458257</v>
       </c>
       <c r="H4" t="n">
-        <v>184.7486281436688</v>
+        <v>173.2254879628375</v>
       </c>
       <c r="I4" t="n">
-        <v>-323.6227321570631</v>
+        <v>-323.6418295132398</v>
       </c>
       <c r="J4" t="n">
-        <v>-321.6714884384817</v>
+        <v>-321.6905857946583</v>
       </c>
     </row>
     <row r="5">
@@ -603,25 +603,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9475816948263461</v>
+        <v>0.9476075371601047</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0317419561294568</v>
+        <v>0.03172354544093593</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00202419550594205</v>
+        <v>0.002023197573336566</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04499106028915133</v>
+        <v>0.0449799685786525</v>
       </c>
       <c r="H5" t="n">
-        <v>260.6577456507338</v>
+        <v>260.3720893867284</v>
       </c>
       <c r="I5" t="n">
-        <v>-300.5343127955997</v>
+        <v>-302.5599552254404</v>
       </c>
       <c r="J5" t="n">
-        <v>-279.070631891204</v>
+        <v>-283.0475180396261</v>
       </c>
     </row>
     <row r="6">
@@ -631,33 +631,33 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>X, V, P, T, dXdt, dVdt, Plag1, X_calc, V_calc</t>
+          <t>X, V, P, T, dXdt, dVdt, Xlag1_calc, Plag1, X_calc, V_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9401099411804392</v>
+        <v>0.927702575013716</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03000271485080064</v>
+        <v>0.03118156572217679</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002312726203404441</v>
+        <v>0.002791851477524935</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04809081204767124</v>
+        <v>0.0528379738211538</v>
       </c>
       <c r="H6" t="n">
-        <v>272.9195562054836</v>
+        <v>229.4521729561451</v>
       </c>
       <c r="I6" t="n">
-        <v>-297.6050703350025</v>
+        <v>-285.8146151437439</v>
       </c>
       <c r="J6" t="n">
-        <v>-280.0438768677697</v>
+        <v>-266.3021779579296</v>
       </c>
     </row>
     <row r="7">
@@ -747,25 +747,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6711629285004654</v>
+        <v>0.6718498465930707</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0790184718289917</v>
+        <v>0.0788194618932328</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01269843655019692</v>
+        <v>0.01267191038702939</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1126873397955463</v>
+        <v>0.1125695802027768</v>
       </c>
       <c r="H9" t="n">
-        <v>1553.669597545979</v>
+        <v>1549.943334575293</v>
       </c>
       <c r="I9" t="n">
-        <v>-201.0463727677339</v>
+        <v>-203.1551108146168</v>
       </c>
       <c r="J9" t="n">
-        <v>-175.6802044261754</v>
+        <v>-179.7401861916397</v>
       </c>
     </row>
     <row r="10">
@@ -775,33 +775,33 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>V, P, Plag1, dXdt_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6521694898259227</v>
+        <v>0.6202163489350336</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07485719602164155</v>
+        <v>0.06512106662155009</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01343189088604445</v>
+        <v>0.01466579961273444</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1158960348158834</v>
+        <v>0.1211024343798854</v>
       </c>
       <c r="H10" t="n">
-        <v>793.3343787358215</v>
+        <v>509.7891604232846</v>
       </c>
       <c r="I10" t="n">
-        <v>-190.1264210990039</v>
+        <v>-193.5563267452383</v>
       </c>
       <c r="J10" t="n">
-        <v>-156.9552778831197</v>
+        <v>-168.1901584036797</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/rP/metrics_global.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,15 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>AIC</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>BIC</t>
         </is>
@@ -483,73 +488,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, T, mu, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9524801128948442</v>
+        <v>0.9521071460715714</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02999834286910062</v>
+        <v>0.02864922095562622</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001835037237515951</v>
+        <v>0.0018494397897011</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04283733462198543</v>
+        <v>0.04300511352968504</v>
       </c>
       <c r="H2" t="n">
-        <v>247.8425504667002</v>
+        <v>19266222.79883258</v>
       </c>
       <c r="I2" t="n">
-        <v>-313.6359062473784</v>
+        <v>0.01666246403131934</v>
       </c>
       <c r="J2" t="n">
-        <v>-299.9772002173085</v>
+        <v>-323.2293701106469</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-319.326882673484</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, Xlag1, Xlag1_calc, Plag1, V_calc, mu_calc, dXdt_calc</t>
+          <t>P, Plag1, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9523220670632249</v>
+        <v>0.9512340424956668</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02923380182802295</v>
+        <v>0.0283004725574129</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001841140366204242</v>
+        <v>0.00188315572770349</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04290851158225186</v>
+        <v>0.04339534223512346</v>
       </c>
       <c r="H3" t="n">
-        <v>168.4311752424794</v>
+        <v>17376551.44489428</v>
       </c>
       <c r="I3" t="n">
-        <v>-307.4632470249061</v>
+        <v>0.01794799626069241</v>
       </c>
       <c r="J3" t="n">
-        <v>-287.9508098390918</v>
+        <v>-318.2899292022781</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-310.4849543279524</v>
       </c>
     </row>
     <row r="4">
@@ -559,33 +570,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>X, V, P, T, I, mu, dXdt, dVdt, Xlag1, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, Plag1, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9506224469700126</v>
+        <v>0.9505028267466032</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03126938980442491</v>
+        <v>0.02857234265657778</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001906773227531814</v>
+        <v>0.001911392497706694</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04366661456458257</v>
+        <v>0.0437194750392396</v>
       </c>
       <c r="H4" t="n">
-        <v>173.2254879628375</v>
+        <v>17761516.96265599</v>
       </c>
       <c r="I4" t="n">
-        <v>-323.6418295132398</v>
+        <v>0.01818712672441371</v>
       </c>
       <c r="J4" t="n">
-        <v>-321.6905857946583</v>
+        <v>-317.5160088005888</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-309.7110339262632</v>
       </c>
     </row>
     <row r="5">
@@ -595,33 +609,36 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P, T, mu, dVdt, Plag1, V_calc, mu_calc</t>
+          <t>P, mu, Plag1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9476075371601047</v>
+        <v>0.9450399060903937</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03172354544093593</v>
+        <v>0.03089736384348083</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002023197573336566</v>
+        <v>0.002122349707412186</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0449799685786525</v>
+        <v>0.04606896685852838</v>
       </c>
       <c r="H5" t="n">
-        <v>260.3720893867284</v>
+        <v>20997544.46095319</v>
       </c>
       <c r="I5" t="n">
-        <v>-302.5599552254404</v>
+        <v>0.01947367296807043</v>
       </c>
       <c r="J5" t="n">
-        <v>-283.0475180396261</v>
+        <v>-314.0720354787548</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-308.2183043230105</v>
       </c>
     </row>
     <row r="6">
@@ -639,25 +656,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.927702575013716</v>
+        <v>0.927714609091555</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03118156572217679</v>
+        <v>0.03117037205053859</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002791851477524935</v>
+        <v>0.002791386755944004</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0528379738211538</v>
+        <v>0.05283357602835535</v>
       </c>
       <c r="H6" t="n">
-        <v>229.4521729561451</v>
+        <v>34841874.27770247</v>
       </c>
       <c r="I6" t="n">
-        <v>-285.8146151437439</v>
+        <v>0.0286395880016943</v>
       </c>
       <c r="J6" t="n">
-        <v>-266.3021779579296</v>
+        <v>-285.8232715976704</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-266.3108344118561</v>
       </c>
     </row>
     <row r="7">
@@ -675,25 +695,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8943651512817544</v>
+        <v>0.8944624436611925</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03463497604045773</v>
+        <v>0.03458508372526666</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00407921594065221</v>
+        <v>0.004075458862662445</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06386873993318022</v>
+        <v>0.0638393206626014</v>
       </c>
       <c r="H7" t="n">
-        <v>244.019790167019</v>
+        <v>18111079.60033093</v>
       </c>
       <c r="I7" t="n">
-        <v>-280.0962249829907</v>
+        <v>0.03601408810550595</v>
       </c>
       <c r="J7" t="n">
-        <v>-274.2424938272464</v>
+        <v>-280.1441405833068</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-274.2904094275625</v>
       </c>
     </row>
     <row r="8">
@@ -711,97 +734,106 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7082285113362289</v>
+        <v>0.7082285126013593</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0654359936207609</v>
+        <v>0.06543599254440344</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0112671047672879</v>
+        <v>0.01126710467289592</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1061466191985779</v>
+        <v>0.1061466187539477</v>
       </c>
       <c r="H8" t="n">
-        <v>795.6060200150993</v>
+        <v>38100689.72710383</v>
       </c>
       <c r="I8" t="n">
-        <v>-231.2651298248304</v>
+        <v>0.09591841949061936</v>
       </c>
       <c r="J8" t="n">
-        <v>-229.313886106249</v>
+        <v>-231.2651302604688</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-229.3138865418874</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, T, dXdt, dXdt_calc, dVdt_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6718498465930707</v>
+        <v>0.6750164673900287</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0788194618932328</v>
+        <v>0.066780906927737</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01267191038702939</v>
+        <v>0.01254962748941002</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1125695802027768</v>
+        <v>0.1120251199035735</v>
       </c>
       <c r="H9" t="n">
-        <v>1549.943334575293</v>
+        <v>34717391.29782642</v>
       </c>
       <c r="I9" t="n">
-        <v>-203.1551108146168</v>
+        <v>0.1067797990255784</v>
       </c>
       <c r="J9" t="n">
-        <v>-179.7401861916397</v>
+        <v>-225.6593433901067</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-223.7080996715253</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>V, P, Plag1, dXdt_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6202163489350336</v>
+        <v>0.6537794936266821</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06512106662155009</v>
+        <v>0.0815717567588634</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01466579961273444</v>
+        <v>0.01336971861092612</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1211024343798854</v>
+        <v>0.115627499371586</v>
       </c>
       <c r="H10" t="n">
-        <v>509.7891604232846</v>
+        <v>69826545.93869965</v>
       </c>
       <c r="I10" t="n">
-        <v>-193.5563267452383</v>
+        <v>0.1137249549396437</v>
       </c>
       <c r="J10" t="n">
-        <v>-168.1901584036797</v>
+        <v>-222.3676725884344</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-220.416428869853</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/rP/metrics_global.xlsx
@@ -488,85 +488,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9521071460715714</v>
+        <v>0.4341167335831847</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02864922095562622</v>
+        <v>0.08741071729936034</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0018494397897011</v>
+        <v>0.0218522586904326</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04300511352968504</v>
+        <v>0.147825094927866</v>
       </c>
       <c r="H2" t="n">
-        <v>19266222.79883258</v>
+        <v>191.8998358736556</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01666246403131934</v>
+        <v>0.1865615610083474</v>
       </c>
       <c r="J2" t="n">
-        <v>-323.2293701106469</v>
+        <v>-192.81945149161</v>
       </c>
       <c r="K2" t="n">
-        <v>-319.326882673484</v>
+        <v>-186.9657203358657</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, Plag1, mu_calc, dXdt_calc</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9512340424956668</v>
+        <v>0.4280894374469226</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0283004725574129</v>
+        <v>0.08511482752039121</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00188315572770349</v>
+        <v>0.02208500993470853</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04339534223512346</v>
+        <v>0.1486102618755129</v>
       </c>
       <c r="H3" t="n">
-        <v>17376551.44489428</v>
+        <v>1054.84616250471</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01794799626069241</v>
+        <v>0.1880326757202192</v>
       </c>
       <c r="J3" t="n">
-        <v>-318.2899292022781</v>
+        <v>-194.2685215728935</v>
       </c>
       <c r="K3" t="n">
-        <v>-310.4849543279524</v>
+        <v>-190.3660341357306</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -574,38 +574,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P, Plag1, mu_calc, dXdt_calc</t>
+          <t>T, X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9505028267466032</v>
+        <v>0.4113924601111596</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02857234265657778</v>
+        <v>0.07676896459706675</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001911392497706694</v>
+        <v>0.0227297836711714</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0437194750392396</v>
+        <v>0.1507639999176574</v>
       </c>
       <c r="H4" t="n">
-        <v>17761516.96265599</v>
+        <v>240.761958954356</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01818712672441371</v>
+        <v>0.1944931105364721</v>
       </c>
       <c r="J4" t="n">
-        <v>-317.5160088005888</v>
+        <v>-188.7721162414464</v>
       </c>
       <c r="K4" t="n">
-        <v>-309.7110339262632</v>
+        <v>-180.9671413671207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -613,155 +613,155 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P, mu, Plag1</t>
+          <t>X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9450399060903937</v>
+        <v>0.2541397587361538</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03089736384348083</v>
+        <v>0.1003350682062156</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002122349707412186</v>
+        <v>0.02880228468710507</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04606896685852838</v>
+        <v>0.1697123586752157</v>
       </c>
       <c r="H5" t="n">
-        <v>20997544.46095319</v>
+        <v>1152.676709125079</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01947367296807043</v>
+        <v>0.2454196716601275</v>
       </c>
       <c r="J5" t="n">
-        <v>-314.0720354787548</v>
+        <v>-178.4596294098104</v>
       </c>
       <c r="K5" t="n">
-        <v>-308.2183043230105</v>
+        <v>-172.6058982540662</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>X, V, P, T, dXdt, dVdt, Xlag1_calc, Plag1, X_calc, V_calc</t>
+          <t>X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.927714609091555</v>
+        <v>0.2164406815035422</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03117037205053859</v>
+        <v>0.08316776228009091</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002791386755944004</v>
+        <v>0.03025807961331663</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05283357602835535</v>
+        <v>0.1739484970136754</v>
       </c>
       <c r="H6" t="n">
-        <v>34841874.27770247</v>
+        <v>625.5213578409335</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0286395880016943</v>
+        <v>0.258748451278259</v>
       </c>
       <c r="J6" t="n">
-        <v>-285.8232715976704</v>
+        <v>-171.8955858467082</v>
       </c>
       <c r="K6" t="n">
-        <v>-266.3108344118561</v>
+        <v>-162.139367253801</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P, T, Plag1</t>
+          <t>X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8944624436611925</v>
+        <v>0.2114946441373274</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03458508372526666</v>
+        <v>0.08345277077785494</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004075458862662445</v>
+        <v>0.03044907675783983</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0638393206626014</v>
+        <v>0.1744966382422304</v>
       </c>
       <c r="H7" t="n">
-        <v>18111079.60033093</v>
+        <v>632.8519456632886</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03601408810550595</v>
+        <v>0.2603659604892897</v>
       </c>
       <c r="J7" t="n">
-        <v>-280.1441405833068</v>
+        <v>-171.5683794717244</v>
       </c>
       <c r="K7" t="n">
-        <v>-274.2904094275625</v>
+        <v>-161.8121608788172</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7082285126013593</v>
+        <v>0.2066011021999797</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06543599254440344</v>
+        <v>0.08576078533513667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01126710467289592</v>
+        <v>0.03063804672863348</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1061466187539477</v>
+        <v>0.1750372723982909</v>
       </c>
       <c r="H8" t="n">
-        <v>38100689.72710383</v>
+        <v>601.0481262061538</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09591841949061936</v>
+        <v>0.2619663020500496</v>
       </c>
       <c r="J8" t="n">
-        <v>-231.2651302604688</v>
+        <v>-171.2466596307792</v>
       </c>
       <c r="K8" t="n">
-        <v>-229.3138865418874</v>
+        <v>-161.490441037872</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -769,71 +769,71 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Xlag1_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6750164673900287</v>
+        <v>-0.1238902743662125</v>
       </c>
       <c r="E9" t="n">
-        <v>0.066780906927737</v>
+        <v>0.1096607267061865</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01254962748941002</v>
+        <v>0.04340036624624592</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1120251199035735</v>
+        <v>0.2083275455772614</v>
       </c>
       <c r="H9" t="n">
-        <v>34717391.29782642</v>
+        <v>1356.112749567165</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1067797990255784</v>
+        <v>0.7360946773644719</v>
       </c>
       <c r="J9" t="n">
-        <v>-225.6593433901067</v>
+        <v>-161.1389447510052</v>
       </c>
       <c r="K9" t="n">
-        <v>-223.7080996715253</v>
+        <v>-159.1877010324238</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T, mu_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6537794936266821</v>
+        <v>-0.2244034842638885</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0815717567588634</v>
+        <v>0.1026092445779059</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01336971861092612</v>
+        <v>0.0472818039823318</v>
       </c>
       <c r="G10" t="n">
-        <v>0.115627499371586</v>
+        <v>0.2174437949961594</v>
       </c>
       <c r="H10" t="n">
-        <v>69826545.93869965</v>
+        <v>981.2350768120831</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1137249549396437</v>
+        <v>0.8028366161335977</v>
       </c>
       <c r="J10" t="n">
-        <v>-222.3676725884344</v>
+        <v>-154.6847470685112</v>
       </c>
       <c r="K10" t="n">
-        <v>-220.416428869853</v>
+        <v>-150.7822596313484</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/rP/metrics_global.xlsx
@@ -500,28 +500,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4341167335831847</v>
+        <v>0.4856203981867561</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08741071729936034</v>
+        <v>0.0832962710464311</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0218522586904326</v>
+        <v>0.01914442167510694</v>
       </c>
       <c r="G2" t="n">
-        <v>0.147825094927866</v>
+        <v>0.1383633682558608</v>
       </c>
       <c r="H2" t="n">
-        <v>191.8998358736556</v>
+        <v>172.5418072773932</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1865615610083474</v>
+        <v>0.1692149757165481</v>
       </c>
       <c r="J2" t="n">
-        <v>-192.81945149161</v>
+        <v>-207.6101707149965</v>
       </c>
       <c r="K2" t="n">
-        <v>-186.9657203358657</v>
+        <v>-201.6432185753037</v>
       </c>
     </row>
     <row r="3">
@@ -531,36 +531,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4280894374469226</v>
+        <v>0.440949418364222</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08511482752039121</v>
+        <v>0.07782983652587949</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02208500993470853</v>
+        <v>0.02080700718850621</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1486102618755129</v>
+        <v>0.1442463420281645</v>
       </c>
       <c r="H3" t="n">
-        <v>1054.84616250471</v>
+        <v>165.0586412651474</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1880326757202192</v>
+        <v>0.1837800795226878</v>
       </c>
       <c r="J3" t="n">
-        <v>-194.2685215728935</v>
+        <v>-203.1131351070171</v>
       </c>
       <c r="K3" t="n">
-        <v>-190.3660341357306</v>
+        <v>-197.1461829673243</v>
       </c>
     </row>
     <row r="4">
@@ -578,28 +578,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4113924601111596</v>
+        <v>0.4072881189933291</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07676896459706675</v>
+        <v>0.07666922522298544</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0227297836711714</v>
+        <v>0.02205982924252374</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1507639999176574</v>
+        <v>0.1485255171427581</v>
       </c>
       <c r="H4" t="n">
-        <v>240.761958954356</v>
+        <v>235.3192590731496</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1944931105364721</v>
+        <v>0.1952554447717679</v>
       </c>
       <c r="J4" t="n">
-        <v>-188.7721162414464</v>
+        <v>-197.9558383120929</v>
       </c>
       <c r="K4" t="n">
-        <v>-180.9671413671207</v>
+        <v>-189.9999021258358</v>
       </c>
     </row>
     <row r="5">
@@ -617,28 +617,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2541397587361538</v>
+        <v>0.2527958558880581</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1003350682062156</v>
+        <v>0.09816428255706189</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02880228468710507</v>
+        <v>0.02780979487102608</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1697123586752157</v>
+        <v>0.1667626902848059</v>
       </c>
       <c r="H5" t="n">
-        <v>1152.676709125079</v>
+        <v>1108.077665767935</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2454196716601275</v>
+        <v>0.2451280996433009</v>
       </c>
       <c r="J5" t="n">
-        <v>-178.4596294098104</v>
+        <v>-187.4478172899144</v>
       </c>
       <c r="K5" t="n">
-        <v>-172.6058982540662</v>
+        <v>-181.4808651502216</v>
       </c>
     </row>
     <row r="6">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2164406815035422</v>
+        <v>0.2188697766654549</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08316776228009091</v>
+        <v>0.08076057814381546</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03025807961331663</v>
+        <v>0.02907247162595776</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1739484970136754</v>
+        <v>0.1705065149076649</v>
       </c>
       <c r="H6" t="n">
-        <v>625.5213578409335</v>
+        <v>609.1727881051906</v>
       </c>
       <c r="I6" t="n">
-        <v>0.258748451278259</v>
+        <v>0.257189797138534</v>
       </c>
       <c r="J6" t="n">
-        <v>-171.8955858467082</v>
+        <v>-181.0500314177346</v>
       </c>
       <c r="K6" t="n">
-        <v>-162.139367253801</v>
+        <v>-171.1051111849132</v>
       </c>
     </row>
     <row r="7">
@@ -695,28 +695,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2114946441373274</v>
+        <v>0.213848225189167</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08345277077785494</v>
+        <v>0.08103746740378254</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03044907675783983</v>
+        <v>0.02925936608792015</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1744966382422304</v>
+        <v>0.1710536935816358</v>
       </c>
       <c r="H7" t="n">
-        <v>632.8519456632886</v>
+        <v>616.3537737623061</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2603659604892897</v>
+        <v>0.258827088704794</v>
       </c>
       <c r="J7" t="n">
-        <v>-171.5683794717244</v>
+        <v>-180.7039996150004</v>
       </c>
       <c r="K7" t="n">
-        <v>-161.8121608788172</v>
+        <v>-170.759079382179</v>
       </c>
     </row>
     <row r="8">
@@ -734,28 +734,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2066011021999797</v>
+        <v>0.2044409046090442</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08576078533513667</v>
+        <v>0.08493654347884995</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03063804672863348</v>
+        <v>0.02960949216481729</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1750372723982909</v>
+        <v>0.1720740891732898</v>
       </c>
       <c r="H8" t="n">
-        <v>601.0481262061538</v>
+        <v>606.7913983048339</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2619663020500496</v>
+        <v>0.2618943731326589</v>
       </c>
       <c r="J8" t="n">
-        <v>-171.2466596307792</v>
+        <v>-180.0616555420389</v>
       </c>
       <c r="K8" t="n">
-        <v>-161.490441037872</v>
+        <v>-170.1167353092175</v>
       </c>
     </row>
     <row r="9">
@@ -773,28 +773,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1238902743662125</v>
+        <v>-0.1213083767796417</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1096607267061865</v>
+        <v>0.106497257305121</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04340036624624592</v>
+        <v>0.0417333819561008</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2083275455772614</v>
+        <v>0.2042874982863631</v>
       </c>
       <c r="H9" t="n">
-        <v>1356.112749567165</v>
+        <v>1290.904731655696</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7360946773644719</v>
+        <v>0.7322117608063262</v>
       </c>
       <c r="J9" t="n">
-        <v>-161.1389447510052</v>
+        <v>-169.5285129707425</v>
       </c>
       <c r="K9" t="n">
-        <v>-159.1877010324238</v>
+        <v>-167.5395289241783</v>
       </c>
     </row>
     <row r="10">
@@ -808,32 +808,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T, mu_calc</t>
+          <t>mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.2244034842638885</v>
+        <v>-0.2356489711549661</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1026092445779059</v>
+        <v>0.1014879080163874</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0472818039823318</v>
+        <v>0.04598896391461386</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2174437949961594</v>
+        <v>0.2144503763452372</v>
       </c>
       <c r="H10" t="n">
-        <v>981.2350768120831</v>
+        <v>358.359525036945</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8028366161335977</v>
+        <v>0.8077739321734391</v>
       </c>
       <c r="J10" t="n">
-        <v>-154.6847470685112</v>
+        <v>-162.2851066135539</v>
       </c>
       <c r="K10" t="n">
-        <v>-150.7822596313484</v>
+        <v>-158.3071385204254</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wnp/rP/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/rP/metrics_global.xlsx
@@ -488,85 +488,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4856203981867561</v>
+        <v>0.9519874956890518</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0832962710464311</v>
+        <v>0.02881089475445594</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01914442167510694</v>
+        <v>0.001854060239705955</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1383633682558608</v>
+        <v>0.04305879979407178</v>
       </c>
       <c r="H2" t="n">
-        <v>172.5418072773932</v>
+        <v>172.0775443916644</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1692149757165481</v>
+        <v>0.01670159346107862</v>
       </c>
       <c r="J2" t="n">
-        <v>-207.6101707149965</v>
+        <v>-323.0996206720078</v>
       </c>
       <c r="K2" t="n">
-        <v>-201.6432185753037</v>
+        <v>-319.197133234845</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, Xlag1_calc</t>
+          <t>P, Plag1, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.440949418364222</v>
+        <v>0.951234072314501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07782983652587949</v>
+        <v>0.02830045314832293</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02080700718850621</v>
+        <v>0.001883154583824586</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1442463420281645</v>
+        <v>0.04339532905537859</v>
       </c>
       <c r="H3" t="n">
-        <v>165.0586412651474</v>
+        <v>165.5032503952965</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1837800795226878</v>
+        <v>0.01794798651432692</v>
       </c>
       <c r="J3" t="n">
-        <v>-203.1131351070171</v>
+        <v>-318.2899607884715</v>
       </c>
       <c r="K3" t="n">
-        <v>-197.1461829673243</v>
+        <v>-310.4849859141458</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -574,38 +574,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc, Xlag1_calc</t>
+          <t>P, Plag1, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4072881189933291</v>
+        <v>0.9505028561306935</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07666922522298544</v>
+        <v>0.02857232127140921</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02205982924252374</v>
+        <v>0.001911391370730069</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1485255171427581</v>
+        <v>0.0437194621505122</v>
       </c>
       <c r="H4" t="n">
-        <v>235.3192590731496</v>
+        <v>160.0681479697605</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1952554447717679</v>
+        <v>0.01818711712030299</v>
       </c>
       <c r="J4" t="n">
-        <v>-197.9558383120929</v>
+        <v>-317.5160394603313</v>
       </c>
       <c r="K4" t="n">
-        <v>-189.9999021258358</v>
+        <v>-309.7110645860056</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -613,155 +613,155 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, Xlag1_calc</t>
+          <t>P, Plag1, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2527958558880581</v>
+        <v>0.945839685144074</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09816428255706189</v>
+        <v>0.02951861074637035</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02780979487102608</v>
+        <v>0.002091465291916267</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1667626902848059</v>
+        <v>0.04573254084255834</v>
       </c>
       <c r="H5" t="n">
-        <v>1108.077665767935</v>
+        <v>154.8129454456337</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2451280996433009</v>
+        <v>0.01921212016111919</v>
       </c>
       <c r="J5" t="n">
-        <v>-187.4478172899144</v>
+        <v>-314.8342988265054</v>
       </c>
       <c r="K5" t="n">
-        <v>-181.4808651502216</v>
+        <v>-308.9805676707611</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, T, Plag1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2188697766654549</v>
+        <v>0.8943651512817544</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08076057814381546</v>
+        <v>0.03463497604045773</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02907247162595776</v>
+        <v>0.00407921594065221</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1705065149076649</v>
+        <v>0.06386873993318022</v>
       </c>
       <c r="H6" t="n">
-        <v>609.1727881051906</v>
+        <v>244.019790167019</v>
       </c>
       <c r="I6" t="n">
-        <v>0.257189797138534</v>
+        <v>0.03604590577393023</v>
       </c>
       <c r="J6" t="n">
-        <v>-181.0500314177346</v>
+        <v>-280.0962249829907</v>
       </c>
       <c r="K6" t="n">
-        <v>-171.1051111849132</v>
+        <v>-274.2424938272464</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, Plag1, X_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.213848225189167</v>
+        <v>0.8449477167095306</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08103746740378254</v>
+        <v>0.04889533151825024</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02925936608792015</v>
+        <v>0.005987529241604896</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1710536935816358</v>
+        <v>0.07737912665315431</v>
       </c>
       <c r="H7" t="n">
-        <v>616.3537737623061</v>
+        <v>616.4705540953979</v>
       </c>
       <c r="I7" t="n">
-        <v>0.258827088704794</v>
+        <v>0.05220695545626425</v>
       </c>
       <c r="J7" t="n">
-        <v>-180.7039996150004</v>
+        <v>-260.1399744890474</v>
       </c>
       <c r="K7" t="n">
-        <v>-170.759079382179</v>
+        <v>-254.2862433333031</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>V_calc, mu_calc, dXdt_calc, dVdt_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2044409046090442</v>
+        <v>0.7082285113362289</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08493654347884995</v>
+        <v>0.0654359936207609</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02960949216481729</v>
+        <v>0.0112671047672879</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1720740891732898</v>
+        <v>0.1061466191985779</v>
       </c>
       <c r="H8" t="n">
-        <v>606.7913983048339</v>
+        <v>795.6060200150993</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2618943731326589</v>
+        <v>0.09591841993623289</v>
       </c>
       <c r="J8" t="n">
-        <v>-180.0616555420389</v>
+        <v>-231.2651298248304</v>
       </c>
       <c r="K8" t="n">
-        <v>-170.1167353092175</v>
+        <v>-229.313886106249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -769,71 +769,71 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1213083767796417</v>
+        <v>0.6750164672087879</v>
       </c>
       <c r="E9" t="n">
-        <v>0.106497257305121</v>
+        <v>0.06678090752283104</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0417333819561008</v>
+        <v>0.01254962754712979</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2042874982863631</v>
+        <v>0.1120251201611933</v>
       </c>
       <c r="H9" t="n">
-        <v>1290.904731655696</v>
+        <v>722.1289232777907</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7322117608063262</v>
+        <v>0.1067797991203545</v>
       </c>
       <c r="J9" t="n">
-        <v>-169.5285129707425</v>
+        <v>-225.659343150942</v>
       </c>
       <c r="K9" t="n">
-        <v>-167.5395289241783</v>
+        <v>-223.7080994323606</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mu_calc, dXdt_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.2356489711549661</v>
+        <v>0.6537795042300654</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1014879080163874</v>
+        <v>0.08157175537987413</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04598896391461386</v>
+        <v>0.01336971825549924</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2144503763452372</v>
+        <v>0.1156274978346381</v>
       </c>
       <c r="H10" t="n">
-        <v>358.359525036945</v>
+        <v>1680.660228523508</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8077739321734391</v>
+        <v>0.1137249515098299</v>
       </c>
       <c r="J10" t="n">
-        <v>-162.2851066135539</v>
+        <v>-222.3676739708268</v>
       </c>
       <c r="K10" t="n">
-        <v>-158.3071385204254</v>
+        <v>-220.4164302522454</v>
       </c>
     </row>
   </sheetData>
